--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T13:19:54+00:00</t>
+    <t>2025-03-05T13:45:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T13:45:25+00:00</t>
+    <t>2025-03-05T16:01:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T16:01:47+00:00</t>
+    <t>2025-03-06T16:40:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T16:40:55+00:00</t>
+    <t>2025-03-09T10:18:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-09T10:18:56+00:00</t>
+    <t>2025-03-09T10:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-09T10:31:47+00:00</t>
+    <t>2025-03-10T07:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T07:49:31+00:00</t>
+    <t>2025-03-10T07:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T07:56:47+00:00</t>
+    <t>2025-03-12T11:31:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:31:39+00:00</t>
+    <t>2025-03-12T11:55:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:55:43+00:00</t>
+    <t>2025-03-12T11:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T11:57:23+00:00</t>
+    <t>2025-03-13T10:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-13T10:18:09+00:00</t>
+    <t>2025-03-18T08:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T08:10:21+00:00</t>
+    <t>2025-03-18T10:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.12.0</t>
+    <t>1.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:21:48+00:00</t>
+    <t>2025-03-18T10:31:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:31:44+00:00</t>
+    <t>2025-03-18T13:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T13:21:59+00:00</t>
+    <t>2025-03-18T14:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:10:18+00:00</t>
+    <t>2025-03-24T10:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:28:29+00:00</t>
+    <t>2025-03-24T10:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:49:00+00:00</t>
+    <t>2025-03-24T11:21:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:21:14+00:00</t>
+    <t>2025-03-24T11:37:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:37:37+00:00</t>
+    <t>2025-04-01T10:33:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:33:26+00:00</t>
+    <t>2025-04-01T10:36:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.0</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:36:45+00:00</t>
+    <t>2025-04-01T10:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T10:40:06+00:00</t>
+    <t>2025-04-01T11:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T11:02:34+00:00</t>
+    <t>2025-04-07T09:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T09:57:36+00:00</t>
+    <t>2025-04-07T10:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T10:44:48+00:00</t>
+    <t>2025-04-07T14:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-07T14:17:30+00:00</t>
+    <t>2025-04-09T20:29:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T20:29:26+00:00</t>
+    <t>2025-04-09T20:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T20:35:07+00:00</t>
+    <t>2025-04-09T22:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-bronsysteem-zorgaanbieder.xlsx
+++ b/ValueSet-bronsysteem-zorgaanbieder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-09T22:25:52+00:00</t>
+    <t>2025-04-09T23:03:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
